--- a/artfynd/A 19109-2022 artfynd.xlsx
+++ b/artfynd/A 19109-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19109-2022 artfynd.xlsx
+++ b/artfynd/A 19109-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101034117</v>
+        <v>101034103</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708430.5260793412</v>
+        <v>708555</v>
       </c>
       <c r="R2" t="n">
-        <v>7086312.260417953</v>
+        <v>7086427</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -791,57 +786,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101034215</v>
+        <v>101824676</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708469.9865216324</v>
+        <v>708328</v>
       </c>
       <c r="R3" t="n">
-        <v>7086584.800897292</v>
+        <v>7086434</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,27 +871,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101034241</v>
+        <v>101824680</v>
       </c>
       <c r="B4" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,46 +894,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>708541.5138680346</v>
+        <v>708488</v>
       </c>
       <c r="R4" t="n">
-        <v>7086488.679000308</v>
+        <v>7086541</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,22 +948,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,69 +968,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101034195</v>
+        <v>101824681</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708550.1325267121</v>
+        <v>708489</v>
       </c>
       <c r="R5" t="n">
-        <v>7086332.611414289</v>
+        <v>7086267</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,22 +1045,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,27 +1065,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101034168</v>
+        <v>101824682</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,41 +1088,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708492.4758918984</v>
+        <v>708413</v>
       </c>
       <c r="R6" t="n">
-        <v>7086553.112880156</v>
+        <v>7086260</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1142,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,46 +1158,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>101034255</v>
+        <v>101824683</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,41 +1185,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708501.7934864035</v>
+        <v>708298</v>
       </c>
       <c r="R7" t="n">
-        <v>7086373.200647124</v>
+        <v>7086391</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,22 +1239,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,27 +1259,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>101034143</v>
+        <v>101034117</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,21 +1282,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1429,21 +1304,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708379.9242182578</v>
+        <v>708431</v>
       </c>
       <c r="R8" t="n">
-        <v>7086353.586007318</v>
+        <v>7086312</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1512,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>101034258</v>
+        <v>101034118</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1556,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708519.5867191976</v>
+        <v>708539</v>
       </c>
       <c r="R9" t="n">
-        <v>7086545.183332293</v>
+        <v>7086312</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1628,15 +1493,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101034121</v>
+        <v>101034119</v>
       </c>
       <c r="B10" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708502.3424307123</v>
+        <v>708507</v>
       </c>
       <c r="R10" t="n">
-        <v>7086478.106574301</v>
+        <v>7086380</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1744,15 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101034253</v>
+        <v>101034120</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,21 +1615,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1788,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>708464.5195341783</v>
+        <v>708471</v>
       </c>
       <c r="R11" t="n">
-        <v>7086300.804961282</v>
+        <v>7086503</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1860,37 +1715,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101034209</v>
+        <v>101034121</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1904,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708479.5770809373</v>
+        <v>708503</v>
       </c>
       <c r="R12" t="n">
-        <v>7086454.024698131</v>
+        <v>7086478</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1976,15 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101034170</v>
+        <v>101034122</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,21 +1837,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2020,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708382.5047902351</v>
+        <v>708471</v>
       </c>
       <c r="R13" t="n">
-        <v>7086321.455427584</v>
+        <v>7086415</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2092,37 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>101034266</v>
+        <v>101034123</v>
       </c>
       <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2136,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708589.562648889</v>
+        <v>708612</v>
       </c>
       <c r="R14" t="n">
-        <v>7086479.046547523</v>
+        <v>7086370</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2208,15 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>101034120</v>
+        <v>101034124</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,10 +2087,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708471.0291907541</v>
+        <v>708578</v>
       </c>
       <c r="R15" t="n">
-        <v>7086502.570923796</v>
+        <v>7086407</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2324,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>101034177</v>
+        <v>101034125</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2340,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2368,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708470.7229978129</v>
+        <v>708576</v>
       </c>
       <c r="R16" t="n">
-        <v>7086440.603371765</v>
+        <v>7086391</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2440,15 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>101034123</v>
+        <v>101034127</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,10 +2309,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708611.9244508692</v>
+        <v>708568</v>
       </c>
       <c r="R17" t="n">
-        <v>7086369.471020069</v>
+        <v>7086376</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2556,15 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>101034256</v>
+        <v>101034128</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2572,21 +2392,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2600,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708549.5539641748</v>
+        <v>708558</v>
       </c>
       <c r="R18" t="n">
-        <v>7086387.885016233</v>
+        <v>7086414</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2672,37 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>101034208</v>
+        <v>101034130</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2716,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708480.5192211071</v>
+        <v>708510</v>
       </c>
       <c r="R19" t="n">
-        <v>7086459.839673454</v>
+        <v>7086551</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2788,57 +2603,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>101034206</v>
+        <v>101824692</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708500.344650572</v>
+        <v>708598</v>
       </c>
       <c r="R20" t="n">
-        <v>7086488.150600363</v>
+        <v>7086386</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2862,22 +2668,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,27 +2688,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>101034130</v>
+        <v>112529804</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,24 +2728,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>708509.4427373735</v>
+        <v>708467</v>
       </c>
       <c r="R21" t="n">
-        <v>7086551.145063997</v>
+        <v>7086429</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2978,22 +2765,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3008,69 +2785,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson, Åsa Stenman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>101034202</v>
+        <v>112529810</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>708407.5356510858</v>
+        <v>708421</v>
       </c>
       <c r="R22" t="n">
-        <v>7086477.991645796</v>
+        <v>7086554</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3094,22 +2862,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,27 +2882,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>101034257</v>
+        <v>101824699</v>
       </c>
       <c r="B23" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3152,41 +2905,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708614.5155258265</v>
+        <v>708516</v>
       </c>
       <c r="R23" t="n">
-        <v>7086390.440878065</v>
+        <v>7086415</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3210,22 +2959,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,27 +2979,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>101034254</v>
+        <v>101824719</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,41 +3002,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708497.9101255394</v>
+        <v>708475</v>
       </c>
       <c r="R24" t="n">
-        <v>7086364.977250649</v>
+        <v>7086519</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3326,22 +3056,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3356,49 +3076,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>101034211</v>
+        <v>101034269</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3412,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708580.5473388685</v>
+        <v>708544</v>
       </c>
       <c r="R25" t="n">
-        <v>7086374.903904772</v>
+        <v>7086493</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3487,12 +3202,7 @@
         <v>101034270</v>
       </c>
       <c r="B26" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3528,10 +3238,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708510.2686745044</v>
+        <v>708510</v>
       </c>
       <c r="R26" t="n">
-        <v>7086565.359041661</v>
+        <v>7086565</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3600,37 +3310,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>101034198</v>
+        <v>101034104</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3644,10 +3349,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708511.1107060825</v>
+        <v>708532</v>
       </c>
       <c r="R27" t="n">
-        <v>7086346.386095176</v>
+        <v>7086304</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3716,37 +3421,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>101034103</v>
+        <v>101034105</v>
       </c>
       <c r="B28" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3760,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708554.9421648593</v>
+        <v>708384</v>
       </c>
       <c r="R28" t="n">
-        <v>7086426.740442511</v>
+        <v>7086489</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3832,15 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>101034109</v>
+        <v>101034107</v>
       </c>
       <c r="B29" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3876,10 +3571,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708487.3599529827</v>
+        <v>708619</v>
       </c>
       <c r="R29" t="n">
-        <v>7086556.754551413</v>
+        <v>7086397</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3948,37 +3643,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>101034118</v>
+        <v>101034108</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3992,10 +3682,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708539.5713140548</v>
+        <v>708613</v>
       </c>
       <c r="R30" t="n">
-        <v>7086311.553178641</v>
+        <v>7086385</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4064,15 +3754,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>101034107</v>
+        <v>101034109</v>
       </c>
       <c r="B31" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4108,10 +3793,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708618.5452622236</v>
+        <v>708488</v>
       </c>
       <c r="R31" t="n">
-        <v>7086396.461684591</v>
+        <v>7086557</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4180,15 +3865,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>101034167</v>
+        <v>101824686</v>
       </c>
       <c r="B32" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4196,41 +3876,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>708428.4655944672</v>
+        <v>708536</v>
       </c>
       <c r="R32" t="n">
-        <v>7086303.273277998</v>
+        <v>7086312</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4254,22 +3930,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4284,27 +3950,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>101034181</v>
+        <v>112529783</v>
       </c>
       <c r="B33" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4312,41 +3973,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708544.0488549111</v>
+        <v>708327</v>
       </c>
       <c r="R33" t="n">
-        <v>7086523.803424856</v>
+        <v>7086298</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4370,22 +4027,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4400,49 +4047,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101034178</v>
+        <v>101034253</v>
       </c>
       <c r="B34" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4456,10 +4098,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708589.562648889</v>
+        <v>708465</v>
       </c>
       <c r="R34" t="n">
-        <v>7086479.046547523</v>
+        <v>7086301</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4528,37 +4170,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101034122</v>
+        <v>101034254</v>
       </c>
       <c r="B35" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4572,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708471.1295630891</v>
+        <v>708498</v>
       </c>
       <c r="R35" t="n">
-        <v>7086414.523760622</v>
+        <v>7086365</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4644,37 +4281,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>101034162</v>
+        <v>101034255</v>
       </c>
       <c r="B36" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4688,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708544.0488549111</v>
+        <v>708502</v>
       </c>
       <c r="R36" t="n">
-        <v>7086523.803424856</v>
+        <v>7086373</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4760,37 +4392,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>101034179</v>
+        <v>101034256</v>
       </c>
       <c r="B37" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4804,10 +4431,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708573.1266029155</v>
+        <v>708550</v>
       </c>
       <c r="R37" t="n">
-        <v>7086492.996344849</v>
+        <v>7086388</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4876,37 +4503,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101034246</v>
+        <v>101034257</v>
       </c>
       <c r="B38" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4920,10 +4542,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708404.5930384785</v>
+        <v>708615</v>
       </c>
       <c r="R38" t="n">
-        <v>7086468.946290102</v>
+        <v>7086391</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4992,37 +4614,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101034161</v>
+        <v>101034258</v>
       </c>
       <c r="B39" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5036,10 +4653,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708573.1266029155</v>
+        <v>708519</v>
       </c>
       <c r="R39" t="n">
-        <v>7086492.996344849</v>
+        <v>7086545</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5108,57 +4725,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>101034125</v>
+        <v>101824717</v>
       </c>
       <c r="B40" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708575.4918707868</v>
+        <v>708525</v>
       </c>
       <c r="R40" t="n">
-        <v>7086390.939558028</v>
+        <v>7086283</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5182,22 +4790,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5212,69 +4810,60 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>101034128</v>
+        <v>101824718</v>
       </c>
       <c r="B41" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708558.4688126111</v>
+        <v>708378</v>
       </c>
       <c r="R41" t="n">
-        <v>7086413.700595979</v>
+        <v>7086234</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5298,22 +4887,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5328,27 +4907,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101034196</v>
+        <v>101824737</v>
       </c>
       <c r="B42" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5356,41 +4930,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708548.2800335612</v>
+        <v>708514</v>
       </c>
       <c r="R42" t="n">
-        <v>7086333.815579799</v>
+        <v>7086423</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5414,22 +4991,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5438,75 +5005,67 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>101034124</v>
+        <v>112529787</v>
       </c>
       <c r="B43" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708578.4058457079</v>
+        <v>708411</v>
       </c>
       <c r="R43" t="n">
-        <v>7086407.063314933</v>
+        <v>7086334</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5530,22 +5089,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5560,49 +5109,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>101034108</v>
+        <v>101034168</v>
       </c>
       <c r="B44" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5616,10 +5160,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708612.6326824062</v>
+        <v>708493</v>
       </c>
       <c r="R44" t="n">
-        <v>7086385.448040312</v>
+        <v>7086553</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5672,6 +5216,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5688,37 +5247,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>101034269</v>
+        <v>101034170</v>
       </c>
       <c r="B45" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5732,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708544.3376116686</v>
+        <v>708382</v>
       </c>
       <c r="R45" t="n">
-        <v>7086492.849315491</v>
+        <v>7086322</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5804,37 +5358,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>101034214</v>
+        <v>101034175</v>
       </c>
       <c r="B46" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5848,10 +5397,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708492.4758918984</v>
+        <v>708432</v>
       </c>
       <c r="R46" t="n">
-        <v>7086553.112880156</v>
+        <v>7086584</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5920,15 +5469,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>101034146</v>
+        <v>101034177</v>
       </c>
       <c r="B47" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5936,21 +5480,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5958,21 +5502,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708557.0303938695</v>
+        <v>708471</v>
       </c>
       <c r="R47" t="n">
-        <v>7086428.649434752</v>
+        <v>7086441</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6041,37 +5580,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>101034201</v>
+        <v>101034178</v>
       </c>
       <c r="B48" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6085,10 +5619,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708500.2891588632</v>
+        <v>708589</v>
       </c>
       <c r="R48" t="n">
-        <v>7086349.205738363</v>
+        <v>7086479</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6157,37 +5691,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>101034159</v>
+        <v>101034179</v>
       </c>
       <c r="B49" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6201,10 +5730,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708469.8407785415</v>
+        <v>708573</v>
       </c>
       <c r="R49" t="n">
-        <v>7086440.544654417</v>
+        <v>7086493</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6273,15 +5802,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>101034119</v>
+        <v>101034181</v>
       </c>
       <c r="B50" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6289,21 +5813,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6317,10 +5841,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708506.6470374305</v>
+        <v>708544</v>
       </c>
       <c r="R50" t="n">
-        <v>7086380.16113243</v>
+        <v>7086524</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6389,57 +5913,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>101034212</v>
+        <v>101824693</v>
       </c>
       <c r="B51" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>708603.9549519499</v>
+        <v>708452</v>
       </c>
       <c r="R51" t="n">
-        <v>7086369.382760704</v>
+        <v>7086582</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6463,22 +5978,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6493,69 +5998,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>101034192</v>
+        <v>101824706</v>
       </c>
       <c r="B52" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>708373.8379576327</v>
+        <v>708526</v>
       </c>
       <c r="R52" t="n">
-        <v>7086358.49104991</v>
+        <v>7086292</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6579,22 +6075,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6609,69 +6095,67 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>101034104</v>
+        <v>101824739</v>
       </c>
       <c r="B53" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708531.6884678493</v>
+        <v>708472</v>
       </c>
       <c r="R53" t="n">
-        <v>7086303.505819481</v>
+        <v>7086445</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6695,22 +6179,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6719,75 +6193,67 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101034105</v>
+        <v>112529785</v>
       </c>
       <c r="B54" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708384.2186987388</v>
+        <v>708374</v>
       </c>
       <c r="R54" t="n">
-        <v>7086488.829624723</v>
+        <v>7086312</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6811,22 +6277,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6841,27 +6297,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101034127</v>
+        <v>112529817</v>
       </c>
       <c r="B55" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6869,41 +6320,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708567.6375472986</v>
+        <v>708430</v>
       </c>
       <c r="R55" t="n">
-        <v>7086375.814251561</v>
+        <v>7086577</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6927,22 +6374,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2022-05-21</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6957,27 +6394,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Simon Mattsson, Anna Hallmén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>101824719</v>
+        <v>112529820</v>
       </c>
       <c r="B56" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6985,21 +6417,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7009,10 +6441,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708474.825739249</v>
+        <v>708441</v>
       </c>
       <c r="R56" t="n">
-        <v>7086518.752697063</v>
+        <v>7086592</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7039,22 +6471,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7069,27 +6491,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>101824717</v>
+        <v>112529821</v>
       </c>
       <c r="B57" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7097,21 +6514,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7121,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708525.0385560611</v>
+        <v>708449</v>
       </c>
       <c r="R57" t="n">
-        <v>7086283.592871366</v>
+        <v>7086593</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7151,22 +6568,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7181,72 +6588,64 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson, Anna Hallmén</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101824739</v>
+        <v>101034158</v>
       </c>
       <c r="B58" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708471.7824421331</v>
+        <v>708432</v>
       </c>
       <c r="R58" t="n">
-        <v>7086444.656239602</v>
+        <v>7086584</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7270,22 +6669,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7294,72 +6693,70 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>101824680</v>
+        <v>101034159</v>
       </c>
       <c r="B59" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708487.5333897375</v>
+        <v>708470</v>
       </c>
       <c r="R59" t="n">
-        <v>7086540.837198208</v>
+        <v>7086441</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7383,22 +6780,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7413,65 +6810,64 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>101824718</v>
+        <v>101034161</v>
       </c>
       <c r="B60" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708378.6027183461</v>
+        <v>708573</v>
       </c>
       <c r="R60" t="n">
-        <v>7086233.579864632</v>
+        <v>7086493</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7495,22 +6891,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7525,27 +6921,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>101824686</v>
+        <v>101034162</v>
       </c>
       <c r="B61" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7553,37 +6944,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708535.5131747238</v>
+        <v>708544</v>
       </c>
       <c r="R61" t="n">
-        <v>7086312.610520432</v>
+        <v>7086524</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7607,22 +7002,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7637,49 +7032,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>101824683</v>
+        <v>112529819</v>
       </c>
       <c r="B62" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7689,10 +7079,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708298.533485498</v>
+        <v>708450</v>
       </c>
       <c r="R62" t="n">
-        <v>7086391.536584749</v>
+        <v>7086586</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7719,22 +7109,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7749,65 +7129,64 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>101824709</v>
+        <v>101034266</v>
       </c>
       <c r="B63" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>708558.986631598</v>
+        <v>708589</v>
       </c>
       <c r="R63" t="n">
-        <v>7086346.033426018</v>
+        <v>7086479</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7831,22 +7210,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7861,49 +7240,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>101824676</v>
+        <v>112529784</v>
       </c>
       <c r="B64" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7913,10 +7287,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708328.0686210667</v>
+        <v>708377</v>
       </c>
       <c r="R64" t="n">
-        <v>7086433.766946083</v>
+        <v>7086312</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7943,22 +7317,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7973,49 +7337,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>101824710</v>
+        <v>112529813</v>
       </c>
       <c r="B65" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8025,10 +7384,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708542.4550735103</v>
+        <v>708426</v>
       </c>
       <c r="R65" t="n">
-        <v>7086321.480230559</v>
+        <v>7086563</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8055,22 +7414,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8085,49 +7434,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>101824706</v>
+        <v>112529822</v>
       </c>
       <c r="B66" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8137,10 +7481,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708525.7753961774</v>
+        <v>708446</v>
       </c>
       <c r="R66" t="n">
-        <v>7086292.492053462</v>
+        <v>7086593</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8167,22 +7511,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8197,65 +7531,69 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Simon Mattsson, Anna Hallmén</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>101824697</v>
+        <v>101034143</v>
       </c>
       <c r="B67" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708561.2643945541</v>
+        <v>708380</v>
       </c>
       <c r="R67" t="n">
-        <v>7086424.948962064</v>
+        <v>7086354</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8279,22 +7617,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8309,27 +7647,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>101824692</v>
+        <v>101034146</v>
       </c>
       <c r="B68" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8337,37 +7670,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>708597.5760019054</v>
+        <v>708557</v>
       </c>
       <c r="R68" t="n">
-        <v>7086385.33028526</v>
+        <v>7086429</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8391,22 +7733,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8421,65 +7763,74 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>101824681</v>
+        <v>101034149</v>
       </c>
       <c r="B69" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708488.9217859493</v>
+        <v>708544</v>
       </c>
       <c r="R69" t="n">
-        <v>7086267.028549808</v>
+        <v>7086493</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8503,22 +7854,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8533,65 +7884,69 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>101824699</v>
+        <v>101034241</v>
       </c>
       <c r="B70" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>708516.2697374942</v>
+        <v>708541</v>
       </c>
       <c r="R70" t="n">
-        <v>7086415.315994384</v>
+        <v>7086489</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8615,22 +7970,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8645,72 +8000,64 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>101824737</v>
+        <v>101034192</v>
       </c>
       <c r="B71" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708513.9774089226</v>
+        <v>708374</v>
       </c>
       <c r="R71" t="n">
-        <v>7086423.12817828</v>
+        <v>7086359</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8734,22 +8081,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8758,34 +8105,28 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>101824711</v>
+        <v>101034195</v>
       </c>
       <c r="B72" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8810,20 +8151,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708313.4711918633</v>
+        <v>708550</v>
       </c>
       <c r="R72" t="n">
-        <v>7086386.777639756</v>
+        <v>7086333</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8847,22 +8192,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8877,65 +8222,64 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>101824682</v>
+        <v>101034196</v>
       </c>
       <c r="B73" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708413.1639170005</v>
+        <v>708548</v>
       </c>
       <c r="R73" t="n">
-        <v>7086260.217162835</v>
+        <v>7086334</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8959,22 +8303,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-06-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8989,27 +8333,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112529796</v>
+        <v>101034198</v>
       </c>
       <c r="B74" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9034,20 +8373,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708427</v>
+        <v>708511</v>
       </c>
       <c r="R74" t="n">
-        <v>7086377</v>
+        <v>7086346</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9071,12 +8414,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9091,27 +8444,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112529811</v>
+        <v>101034201</v>
       </c>
       <c r="B75" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9136,20 +8484,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>708445</v>
+        <v>708500</v>
       </c>
       <c r="R75" t="n">
-        <v>7086554</v>
+        <v>7086349</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9173,12 +8525,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9193,27 +8555,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112529802</v>
+        <v>101034202</v>
       </c>
       <c r="B76" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9238,20 +8595,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>708527</v>
+        <v>708407</v>
       </c>
       <c r="R76" t="n">
-        <v>7086401</v>
+        <v>7086478</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9275,12 +8636,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9295,65 +8666,64 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Anna Hallmén</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112529787</v>
+        <v>101034204</v>
       </c>
       <c r="B77" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>708411</v>
+        <v>708382</v>
       </c>
       <c r="R77" t="n">
-        <v>7086334</v>
+        <v>7086513</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9377,12 +8747,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9397,65 +8777,64 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112529809</v>
+        <v>101034206</v>
       </c>
       <c r="B78" t="n">
-        <v>103945</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708479</v>
+        <v>708501</v>
       </c>
       <c r="R78" t="n">
-        <v>7086518</v>
+        <v>7086488</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9479,12 +8858,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9499,27 +8888,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112529792</v>
+        <v>101034208</v>
       </c>
       <c r="B79" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9544,20 +8928,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708438</v>
+        <v>708481</v>
       </c>
       <c r="R79" t="n">
-        <v>7086354</v>
+        <v>7086460</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9581,12 +8969,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9601,65 +8999,64 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112529804</v>
+        <v>101034209</v>
       </c>
       <c r="B80" t="n">
-        <v>89661</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708467</v>
+        <v>708480</v>
       </c>
       <c r="R80" t="n">
-        <v>7086429</v>
+        <v>7086454</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9683,12 +9080,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9703,27 +9110,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Åsa Stenman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112529795</v>
+        <v>101034211</v>
       </c>
       <c r="B81" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9748,20 +9150,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>708433</v>
+        <v>708581</v>
       </c>
       <c r="R81" t="n">
-        <v>7086376</v>
+        <v>7086375</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9785,12 +9191,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9805,27 +9221,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112529800</v>
+        <v>101034212</v>
       </c>
       <c r="B82" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9850,20 +9261,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>708496</v>
+        <v>708604</v>
       </c>
       <c r="R82" t="n">
-        <v>7086401</v>
+        <v>7086370</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9887,12 +9302,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9907,27 +9332,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Anna Hallmén</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112529808</v>
+        <v>101034214</v>
       </c>
       <c r="B83" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9952,20 +9372,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708522</v>
+        <v>708493</v>
       </c>
       <c r="R83" t="n">
-        <v>7086517</v>
+        <v>7086553</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9989,12 +9413,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10009,27 +9443,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Henrik Sporrong</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112529799</v>
+        <v>101034215</v>
       </c>
       <c r="B84" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10054,20 +9483,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Rågberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708445</v>
+        <v>708470</v>
       </c>
       <c r="R84" t="n">
-        <v>7086400</v>
+        <v>7086585</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10091,12 +9524,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10111,27 +9554,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112529790</v>
+        <v>101824709</v>
       </c>
       <c r="B85" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10163,10 +9601,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708430</v>
+        <v>708559</v>
       </c>
       <c r="R85" t="n">
-        <v>7086348</v>
+        <v>7086346</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10193,12 +9631,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10213,27 +9651,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112529788</v>
+        <v>101824710</v>
       </c>
       <c r="B86" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10265,10 +9698,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708503</v>
+        <v>708542</v>
       </c>
       <c r="R86" t="n">
-        <v>7086342</v>
+        <v>7086322</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10295,12 +9728,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10315,27 +9748,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Anna Hallmén</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112529803</v>
+        <v>101824711</v>
       </c>
       <c r="B87" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10367,10 +9795,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708494</v>
+        <v>708314</v>
       </c>
       <c r="R87" t="n">
-        <v>7086416</v>
+        <v>7086387</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10397,12 +9825,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2022-06-21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10417,27 +9845,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112529789</v>
+        <v>112529788</v>
       </c>
       <c r="B88" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10469,10 +9892,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>708428</v>
+        <v>708503</v>
       </c>
       <c r="R88" t="n">
-        <v>7086347</v>
+        <v>7086342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10531,15 +9954,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112529806</v>
+        <v>112529789</v>
       </c>
       <c r="B89" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10571,10 +9989,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>708467</v>
+        <v>708428</v>
       </c>
       <c r="R89" t="n">
-        <v>7086430</v>
+        <v>7086347</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10626,22 +10044,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Simon Mattsson, Anna Hallmén</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>112529801</v>
+        <v>112529790</v>
       </c>
       <c r="B90" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10673,10 +10086,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>708492</v>
+        <v>708430</v>
       </c>
       <c r="R90" t="n">
-        <v>7086401</v>
+        <v>7086348</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10728,44 +10141,39 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>112529783</v>
+        <v>112529791</v>
       </c>
       <c r="B91" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10775,10 +10183,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>708327</v>
+        <v>708431</v>
       </c>
       <c r="R91" t="n">
-        <v>7086298</v>
+        <v>7086350</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10830,22 +10238,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Simon Mattsson, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>112529798</v>
+        <v>112529792</v>
       </c>
       <c r="B92" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10877,10 +10280,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708447</v>
+        <v>708438</v>
       </c>
       <c r="R92" t="n">
-        <v>7086397</v>
+        <v>7086355</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10939,37 +10342,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>112529784</v>
+        <v>112529793</v>
       </c>
       <c r="B93" t="n">
-        <v>78842</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10979,10 +10377,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708377</v>
+        <v>708436</v>
       </c>
       <c r="R93" t="n">
-        <v>7086312</v>
+        <v>7086358</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11041,37 +10439,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>112529785</v>
+        <v>112529794</v>
       </c>
       <c r="B94" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11081,10 +10474,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708373</v>
+        <v>708458</v>
       </c>
       <c r="R94" t="n">
-        <v>7086312</v>
+        <v>7086358</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11136,22 +10529,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Simon Mattsson</t>
+          <t>Simon Mattsson, Henrik Sporrong</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>112529797</v>
+        <v>112529795</v>
       </c>
       <c r="B95" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11183,10 +10571,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708425</v>
+        <v>708433</v>
       </c>
       <c r="R95" t="n">
-        <v>7086380</v>
+        <v>7086376</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11245,15 +10633,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>112529791</v>
+        <v>112529796</v>
       </c>
       <c r="B96" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11285,10 +10668,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708431</v>
+        <v>708427</v>
       </c>
       <c r="R96" t="n">
-        <v>7086350</v>
+        <v>7086377</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11340,22 +10723,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Henrik Sporrong</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112529794</v>
+        <v>112529797</v>
       </c>
       <c r="B97" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11387,10 +10765,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>708458</v>
+        <v>708425</v>
       </c>
       <c r="R97" t="n">
-        <v>7086357</v>
+        <v>7086380</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11442,22 +10820,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Henrik Sporrong</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112529793</v>
+        <v>112529798</v>
       </c>
       <c r="B98" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11489,10 +10862,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>708436</v>
+        <v>708448</v>
       </c>
       <c r="R98" t="n">
-        <v>7086358</v>
+        <v>7086398</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11544,10 +10917,1091 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>112529799</v>
+      </c>
+      <c r="B99" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>708445</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7086401</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
           <t>Simon Mattsson</t>
         </is>
       </c>
-      <c r="AY98" t="inlineStr"/>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>112529800</v>
+      </c>
+      <c r="B100" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>708497</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7086401</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>112529801</v>
+      </c>
+      <c r="B101" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>708492</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7086401</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>112529802</v>
+      </c>
+      <c r="B102" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>708526</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7086402</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>112529803</v>
+      </c>
+      <c r="B103" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>708494</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7086416</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>112529806</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>708467</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7086430</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>112529808</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>708522</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7086516</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Henrik Sporrong</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>112529811</v>
+      </c>
+      <c r="B106" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>708446</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7086554</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>112529809</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>708479</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7086518</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Simon Mattsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Simon Mattsson, Maja Östlund</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>101034167</v>
+      </c>
+      <c r="B108" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>708429</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7086303</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2022-05-21</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Jon Andersson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>101824697</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Rågberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>708561</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7086425</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2022-06-21</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2022-06-21</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19109-2022 artfynd.xlsx
+++ b/artfynd/A 19109-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AZ109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034103</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824676</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824680</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824681</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824682</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824683</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034117</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034118</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034119</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1712,6 +1762,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034120</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1823,6 +1878,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034121</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1934,6 +1994,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034122</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2045,6 +2110,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034123</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034124</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034125</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034127</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2489,6 +2574,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034128</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2600,6 +2690,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034130</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2697,6 +2792,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824692</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2794,6 +2894,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529804</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2891,6 +2996,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529810</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2988,6 +3098,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824699</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3085,6 +3200,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824719</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3196,6 +3316,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034269</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3307,6 +3432,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034270</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3418,6 +3548,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034104</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3529,6 +3664,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034105</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3640,6 +3780,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034107</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3751,6 +3896,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034108</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3862,6 +4012,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034109</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3959,6 +4114,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824686</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4056,6 +4216,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529783</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4167,6 +4332,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034253</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4278,6 +4448,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034254</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4389,6 +4564,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034255</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4500,6 +4680,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034256</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4611,6 +4796,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034257</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4722,6 +4912,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034258</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4819,6 +5014,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824717</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4916,6 +5116,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824718</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5021,6 +5226,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824737</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5118,6 +5328,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529787</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5244,6 +5459,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034168</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5355,6 +5575,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034170</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5466,6 +5691,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034175</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5577,6 +5807,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034177</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5688,6 +5923,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034178</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5799,6 +6039,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034179</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5910,6 +6155,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034181</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6007,6 +6257,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824693</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6104,6 +6359,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824706</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6209,6 +6469,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824739</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6306,6 +6571,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529785</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6403,6 +6673,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529817</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6500,6 +6775,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529820</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6597,6 +6877,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529821</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6708,6 +6993,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034158</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6819,6 +7109,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034159</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6930,6 +7225,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034161</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7041,6 +7341,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034162</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7138,6 +7443,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529819</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7249,6 +7559,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034266</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7346,6 +7661,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529784</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7443,6 +7763,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529813</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7540,6 +7865,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529822</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7656,6 +7986,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034143</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7772,6 +8107,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034146</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7893,6 +8233,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034149</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8009,6 +8354,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034241</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8120,6 +8470,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034192</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8231,6 +8586,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034195</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8342,6 +8702,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034196</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8453,6 +8818,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034198</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8564,6 +8934,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034201</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8675,6 +9050,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034202</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8786,6 +9166,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034204</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8897,6 +9282,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034206</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9008,6 +9398,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034208</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9119,6 +9514,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034209</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9230,6 +9630,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034211</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9341,6 +9746,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034212</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9452,6 +9862,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034214</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9563,6 +9978,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034215</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9660,6 +10080,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824709</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9757,6 +10182,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824710</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9854,6 +10284,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824711</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9951,6 +10386,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529788</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10048,6 +10488,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529789</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10145,6 +10590,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529790</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10242,6 +10692,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529791</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10339,6 +10794,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529792</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10436,6 +10896,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529793</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10533,6 +10998,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529794</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10630,6 +11100,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529795</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10727,6 +11202,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529796</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10824,6 +11304,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529797</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10921,6 +11406,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529798</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11018,6 +11508,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529799</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11115,6 +11610,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529800</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11212,6 +11712,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529801</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11309,6 +11814,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529802</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11406,6 +11916,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529803</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11503,6 +12018,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529806</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11600,6 +12120,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529808</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11697,6 +12222,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529811</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11794,6 +12324,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112529809</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11905,6 +12440,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101034167</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12002,8 +12542,123 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101824697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>